--- a/docs/dataroom/sold-direct-model.xlsx
+++ b/docs/dataroom/sold-direct-model.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Home" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="P&amp;L (Base)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="COGS Build" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Scenarios" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Market Sizing" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Capital &amp; Valuation" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Use of Funds" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Cap Table" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Competitive Landscape" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Ancillary Revenue" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Notes &amp; Sources" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L (Base)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COGS Build" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market Sizing" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capital &amp; Valuation" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Use of Funds" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cap Table" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitive Landscape" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ancillary Revenue" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes &amp; Sources" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C19" s="124" t="inlineStr">
         <is>
-          <t>How the R10m raise is allocated</t>
+          <t>How the R5m raise is allocated</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="B1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="117" min="2" max="3"/>
@@ -1672,7 +1672,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="118">
       <c r="B4" s="220" t="inlineStr">
         <is>
@@ -2008,7 +2007,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="117" t="inlineStr">
         <is>
           <t>NOTE: Traditional agents serve the full-service segment - complementary, not a target. Sold Direct serves sellers who choose to sell privately, assisted by our own employed, registered practitioners (PPRA/FFC).</t>
         </is>
@@ -2724,7 +2723,7 @@
     <row r="5" ht="15" customHeight="1" s="118">
       <c r="B5" s="136" t="inlineStr">
         <is>
-          <t>Bond origination referral (% of bond, via ooba — Y1 only)</t>
+          <t>Bond origination referral (% of bond, via BetterBond — Y1 only)</t>
         </is>
       </c>
       <c r="C5" s="137" t="n">
@@ -3290,7 +3289,7 @@
     <row r="40" ht="15" customHeight="1" s="118">
       <c r="B40" s="135" t="inlineStr">
         <is>
-          <t>OPERATING EXPENSE INPUTS (BASE)</t>
+          <t>OPERATING EXPENSE INPUTS (BASE) — Y1–Y2 on the bootstrap operating stance (Oct 2026): four-person team, no office, Paysoft free-dev allocation</t>
         </is>
       </c>
       <c r="C40" s="135" t="n"/>
@@ -3334,10 +3333,10 @@
         </is>
       </c>
       <c r="C42" s="146" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" s="146" t="n">
         <v>8</v>
-      </c>
-      <c r="D42" s="146" t="n">
-        <v>14</v>
       </c>
       <c r="E42" s="146" t="n">
         <v>22</v>
@@ -3356,10 +3355,10 @@
         </is>
       </c>
       <c r="C43" s="137" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D43" s="137" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E43" s="137" t="n">
         <v>0.5</v>
@@ -3428,14 +3427,14 @@
     <row r="46" ht="15" customHeight="1" s="118">
       <c r="B46" s="136" t="inlineStr">
         <is>
-          <t>Human fully-loaded cost / FTE (R/yr)</t>
+          <t>Human fully-loaded cost / FTE (R/yr) — Y1–Y2 bootstrap team: MD R50k · Marketing Director R50k · principal practitioner &amp; compliance R30k · agent/admin R20k per month, + statutory; Y2 adds 2 practitioners (R30k) + 2 agent/admin (R20k) against mandates</t>
         </is>
       </c>
       <c r="C46" s="140" t="n">
-        <v>700000</v>
+        <v>462500</v>
       </c>
       <c r="D46" s="140" t="n">
-        <v>722000</v>
+        <v>381250</v>
       </c>
       <c r="E46" s="140" t="n">
         <v>738000</v>
@@ -3525,10 +3524,10 @@
         </is>
       </c>
       <c r="C50" s="140" t="n">
-        <v>600000</v>
+        <v>450000</v>
       </c>
       <c r="D50" s="140" t="n">
-        <v>1000000</v>
+        <v>900000</v>
       </c>
       <c r="E50" s="140" t="n">
         <v>1800000</v>
@@ -3569,10 +3568,10 @@
         </is>
       </c>
       <c r="C52" s="140" t="n">
-        <v>600000</v>
+        <v>350000</v>
       </c>
       <c r="D52" s="140" t="n">
-        <v>1000000</v>
+        <v>850000</v>
       </c>
       <c r="E52" s="140" t="n">
         <v>1800000</v>
@@ -6091,7 +6090,7 @@
     <row r="43" ht="15" customHeight="1" s="118">
       <c r="B43" s="185" t="inlineStr">
         <is>
-          <t>CASH RUNWAY CHECK (Base scenario — does Series A timing cover the trough?)</t>
+          <t>CASH RUNWAY CHECK (Base scenario — does the R5m seed cover the trough before the optional Series A?)</t>
         </is>
       </c>
     </row>
@@ -7118,11 +7117,11 @@
     <row r="9" ht="15" customHeight="1" s="118">
       <c r="B9" s="136" t="inlineStr">
         <is>
-          <t>Seed round (R) — growth buffer above need</t>
+          <t>Seed round (R) — lean R5m seed (Oct 2026)</t>
         </is>
       </c>
       <c r="C9" s="209" t="n">
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="118">
@@ -7242,7 +7241,7 @@
         </is>
       </c>
       <c r="C20" s="209" t="n">
-        <v>40000000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="118">
@@ -7379,7 +7378,7 @@
         </is>
       </c>
       <c r="C5" s="212" t="n">
-        <v>3300000</v>
+        <v>2000000</v>
       </c>
       <c r="D5" s="165">
         <f>C5/$C$11</f>
@@ -7387,18 +7386,18 @@
       </c>
       <c r="E5" s="213" t="inlineStr">
         <is>
-          <t>First brand campaign in prime CT — the deal-ramp engine; prove ATL→deals conversion</t>
+          <t>Cape Town launch + brand campaign in prime CT — the deal-ramp engine; prove ATL→deals conversion</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="118">
       <c r="B6" s="192" t="inlineStr">
         <is>
-          <t>Team (AI-augmented, ~8 people)</t>
+          <t>Team (four people: founders, principal practitioner, agent/admin)</t>
         </is>
       </c>
       <c r="C6" s="212" t="n">
-        <v>3300000</v>
+        <v>1200000</v>
       </c>
       <c r="D6" s="165">
         <f>C6/$C$11</f>
@@ -7406,7 +7405,7 @@
       </c>
       <c r="E6" s="213" t="inlineStr">
         <is>
-          <t>Founders + small human core (product, ops/concierge, partnerships); 12–18mo runway</t>
+          <t>Four-person bootstrap team at R150k/month — founders at R50k each carry marketing, management, dealmaking, bookkeeping and tech support; hires beyond four only against signed mandates</t>
         </is>
       </c>
     </row>
@@ -7417,7 +7416,7 @@
         </is>
       </c>
       <c r="C7" s="212" t="n">
-        <v>1300000</v>
+        <v>500000</v>
       </c>
       <c r="D7" s="165">
         <f>C7/$C$11</f>
@@ -7425,7 +7424,7 @@
       </c>
       <c r="E7" s="213" t="inlineStr">
         <is>
-          <t>WhatsApp Cloud API/BSP, AI agents, deal tracker, dashboard, security</t>
+          <t>WhatsApp BSP, deal tracker, dashboard, security — Paysoft free-development allocation carries most of the build</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7435,7 @@
         </is>
       </c>
       <c r="C8" s="212" t="n">
-        <v>700000</v>
+        <v>400000</v>
       </c>
       <c r="D8" s="165">
         <f>C8/$C$11</f>
@@ -7444,7 +7443,7 @@
       </c>
       <c r="E8" s="213" t="inlineStr">
         <is>
-          <t>ooba + panel conveyancers live; secure the bank headline sponsor; onboarding</t>
+          <t>BetterBond + panel conveyancers live; secure the bank headline sponsor; Property24 feed</t>
         </is>
       </c>
     </row>
@@ -7455,7 +7454,7 @@
         </is>
       </c>
       <c r="C9" s="212" t="n">
-        <v>700000</v>
+        <v>500000</v>
       </c>
       <c r="D9" s="165">
         <f>C9/$C$11</f>
@@ -7463,7 +7462,7 @@
       </c>
       <c r="E9" s="213" t="inlineStr">
         <is>
-          <t>PPRA practitioner + FFC, POPIA programme, contracts, mandate templates</t>
+          <t>PPRA practitioner + FFC, POPIA programme, contracts, mandate templates, FAIS/FSP groundwork</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7473,7 @@
         </is>
       </c>
       <c r="C10" s="212" t="n">
-        <v>700000</v>
+        <v>400000</v>
       </c>
       <c r="D10" s="165">
         <f>C10/$C$11</f>
@@ -7482,7 +7481,7 @@
       </c>
       <c r="E10" s="213" t="inlineStr">
         <is>
-          <t>Buffer above the ~R6m modelled cash low-point</t>
+          <t>Buffer above the modelled Y1 cash trough</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7525,7 @@
     <row r="15" ht="15" customHeight="1" s="118">
       <c r="B15" s="134" t="inlineStr">
         <is>
-          <t>Note: survival need is only ~R6m; the rest is growth capital (brand + team) to drive the deal ramp.</t>
+          <t>Note: the bootstrap stance (four-person team, no office) keeps the modelled cash trough small; most of the R5m is launch marketing and runway headroom in every scenario.</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B1:E32"/>
+  <dimension ref="B1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="117" min="2" max="2"/>
@@ -7561,7 +7560,7 @@
     <row r="2" ht="15" customHeight="1" s="118">
       <c r="B2" s="134" t="inlineStr">
         <is>
-          <t>No separate founding round — funder invests at inception alongside founders. Three working founders hold 25% each; Jan le Roux holds 5% (board / non-executive, vesting); Strategic Funder invests R10m for 20% (R40m pre / R50m post). Working-founder equity vests 4 years, 1-year cliff. Amber = editable inputs; round economics linked from Capital &amp; Valuation.</t>
+          <t>No separate founding round — the Strategic Funder and the technology partner come in at inception alongside the working founders. Johannes le Roux 32.5% · Dean Kruger 32.5% · Paysoft (technology partner, vesting against preferred rates + free development) 10% · option pool (reserved) 4% · board seat (reserved, non-executive) 1% · Strategic Funder R5m for 20% (R20m pre / R25m post). Founder shares reverse-vest over 36 months. Amber = editable inputs; round economics linked from Capital &amp; Valuation.</t>
         </is>
       </c>
     </row>
@@ -7691,11 +7690,11 @@
     <row r="16" ht="15" customHeight="1" s="118">
       <c r="B16" s="192" t="inlineStr">
         <is>
-          <t>Johannes — Commercial Director</t>
+          <t>Johannes le Roux — Marketing Director</t>
         </is>
       </c>
       <c r="C16" s="216" t="n">
-        <v>0.25</v>
+        <v>0.325</v>
       </c>
       <c r="D16" s="217">
         <f>C16*($C$8/$C$10)</f>
@@ -7705,11 +7704,11 @@
     <row r="17" ht="15" customHeight="1" s="118">
       <c r="B17" s="192" t="inlineStr">
         <is>
-          <t>Wilhelm — CTO</t>
+          <t>Dean Kruger — Managing Director</t>
         </is>
       </c>
       <c r="C17" s="216" t="n">
-        <v>0.25</v>
+        <v>0.325</v>
       </c>
       <c r="D17" s="217">
         <f>C17*($C$8/$C$10)</f>
@@ -7719,11 +7718,11 @@
     <row r="18" ht="15" customHeight="1" s="118">
       <c r="B18" s="192" t="inlineStr">
         <is>
-          <t>Dean — COO</t>
+          <t>Paysoft — Technology Partner (vesting)</t>
         </is>
       </c>
       <c r="C18" s="216" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="D18" s="217">
         <f>C18*($C$8/$C$10)</f>
@@ -7733,11 +7732,11 @@
     <row r="19" ht="15" customHeight="1" s="118">
       <c r="B19" s="192" t="inlineStr">
         <is>
-          <t>Jan le Roux — Board (non-executive)</t>
+          <t>Option pool (reserved, unissued)</t>
         </is>
       </c>
       <c r="C19" s="216" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D19" s="217">
         <f>C19*($C$8/$C$10)</f>
@@ -7747,12 +7746,11 @@
     <row r="20" ht="15" customHeight="1" s="118">
       <c r="B20" s="192" t="inlineStr">
         <is>
-          <t>Strategic Funder / Seed Investor</t>
-        </is>
-      </c>
-      <c r="C20" s="218">
-        <f>$C$6/$C$7</f>
-        <v/>
+          <t>Board seat (reserved, non-executive)</t>
+        </is>
+      </c>
+      <c r="C20" s="216" t="n">
+        <v>0.01</v>
       </c>
       <c r="D20" s="217">
         <f>C20*($C$8/$C$10)</f>
@@ -7762,193 +7760,233 @@
     <row r="21" ht="15" customHeight="1" s="118">
       <c r="B21" s="192" t="inlineStr">
         <is>
+          <t>Strategic Funder / Seed Investor</t>
+        </is>
+      </c>
+      <c r="C21" s="216">
+        <f>$C$6/$C$7</f>
+        <v/>
+      </c>
+      <c r="D21" s="217">
+        <f>C21*($C$8/$C$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="118">
+      <c r="B22" s="192" t="inlineStr">
+        <is>
           <t>Series A Investor</t>
         </is>
       </c>
-      <c r="C21" s="218" t="n">
+      <c r="C22" s="216" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="217">
+      <c r="D22" s="217">
         <f>$C$9/$C$10</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="118">
-      <c r="B22" s="189" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="189" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C22" s="219">
-        <f>SUM(C16:C21)</f>
-        <v/>
-      </c>
-      <c r="D22" s="219">
-        <f>SUM(D16:D21)</f>
+      <c r="C23" s="219">
+        <f>SUM(C16:C22)</f>
+        <v/>
+      </c>
+      <c r="D23" s="219">
+        <f>SUM(D16:D22)</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="118">
-      <c r="B24" s="211" t="inlineStr">
-        <is>
-          <t>VALUE OF STAKE (R)</t>
-        </is>
-      </c>
+      <c r="B24" s="211" t="n"/>
       <c r="C24" s="211" t="n"/>
       <c r="D24" s="211" t="n"/>
       <c r="E24" s="211" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="118">
-      <c r="B25" s="198" t="inlineStr">
+      <c r="B25" s="211" t="inlineStr">
+        <is>
+          <t>VALUE OF STAKE (R)</t>
+        </is>
+      </c>
+      <c r="C25" s="198" t="n"/>
+      <c r="D25" s="198" t="n"/>
+      <c r="E25" s="198" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="118">
+      <c r="B26" s="198" t="inlineStr">
         <is>
           <t>Holder</t>
         </is>
       </c>
-      <c r="C25" s="198">
+      <c r="C26" s="198">
         <f>"At Seed (R"&amp;TEXT(C7/1000000,"0")&amp;"m)"</f>
         <v/>
       </c>
-      <c r="D25" s="198" t="inlineStr">
+      <c r="D26" s="198" t="inlineStr">
         <is>
           <t>At Series A</t>
         </is>
       </c>
-      <c r="E25" s="198" t="inlineStr">
+      <c r="E26" s="198" t="inlineStr">
         <is>
           <t>At Exit</t>
         </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="118">
-      <c r="B26" s="192" t="inlineStr">
-        <is>
-          <t>Johannes — Commercial Director</t>
-        </is>
-      </c>
-      <c r="C26" s="164">
-        <f>C16*$C$7</f>
-        <v/>
-      </c>
-      <c r="D26" s="164">
-        <f>D16*$C$10</f>
-        <v/>
-      </c>
-      <c r="E26" s="179">
-        <f>D16*$C$12</f>
-        <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="118">
       <c r="B27" s="192" t="inlineStr">
         <is>
-          <t>Wilhelm — CTO</t>
+          <t>Johannes le Roux — Marketing Director</t>
         </is>
       </c>
       <c r="C27" s="164">
-        <f>C17*$C$7</f>
+        <f>C16*$C$7</f>
         <v/>
       </c>
       <c r="D27" s="164">
-        <f>D17*$C$10</f>
+        <f>D16*$C$10</f>
         <v/>
       </c>
       <c r="E27" s="179">
-        <f>D17*$C$12</f>
+        <f>D16*$C$12</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="118">
       <c r="B28" s="192" t="inlineStr">
         <is>
-          <t>Dean — COO</t>
+          <t>Dean Kruger — Managing Director</t>
         </is>
       </c>
       <c r="C28" s="164">
-        <f>C18*$C$7</f>
+        <f>C17*$C$7</f>
         <v/>
       </c>
       <c r="D28" s="164">
-        <f>D18*$C$10</f>
+        <f>D17*$C$10</f>
         <v/>
       </c>
       <c r="E28" s="179">
-        <f>D18*$C$12</f>
+        <f>D17*$C$12</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="118">
       <c r="B29" s="192" t="inlineStr">
         <is>
-          <t>Jan le Roux — Board (non-executive)</t>
+          <t>Paysoft — Technology Partner (vesting)</t>
         </is>
       </c>
       <c r="C29" s="164">
-        <f>C19*$C$7</f>
+        <f>C18*$C$7</f>
         <v/>
       </c>
       <c r="D29" s="164">
-        <f>D19*$C$10</f>
+        <f>D18*$C$10</f>
         <v/>
       </c>
       <c r="E29" s="179">
-        <f>D19*$C$12</f>
+        <f>D18*$C$12</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="118">
       <c r="B30" s="192" t="inlineStr">
         <is>
-          <t>Strategic Funder / Seed Investor</t>
+          <t>Option pool (reserved, unissued)</t>
         </is>
       </c>
       <c r="C30" s="164">
-        <f>C20*$C$7</f>
+        <f>C19*$C$7</f>
         <v/>
       </c>
       <c r="D30" s="164">
-        <f>D20*$C$10</f>
+        <f>D19*$C$10</f>
         <v/>
       </c>
       <c r="E30" s="179">
-        <f>D20*$C$12</f>
+        <f>D19*$C$12</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="118">
       <c r="B31" s="192" t="inlineStr">
         <is>
+          <t>Board seat (reserved, non-executive)</t>
+        </is>
+      </c>
+      <c r="C31" s="164">
+        <f>C20*$C$7</f>
+        <v/>
+      </c>
+      <c r="D31" s="164">
+        <f>D20*$C$10</f>
+        <v/>
+      </c>
+      <c r="E31" s="179">
+        <f>D20*$C$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="118">
+      <c r="B32" s="192" t="inlineStr">
+        <is>
+          <t>Strategic Funder / Seed Investor</t>
+        </is>
+      </c>
+      <c r="C32" s="164">
+        <f>C21*$C$7</f>
+        <v/>
+      </c>
+      <c r="D32" s="164">
+        <f>D21*$C$10</f>
+        <v/>
+      </c>
+      <c r="E32" s="179">
+        <f>D21*$C$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="192" t="inlineStr">
+        <is>
           <t>Series A Investor</t>
         </is>
       </c>
-      <c r="C31" s="164">
-        <f>C21*$C$7</f>
-        <v/>
-      </c>
-      <c r="D31" s="164">
-        <f>D21*$C$10</f>
-        <v/>
-      </c>
-      <c r="E31" s="179">
-        <f>D21*$C$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="118">
-      <c r="B32" s="189" t="inlineStr">
+      <c r="C33" s="164">
+        <f>C22*$C$7</f>
+        <v/>
+      </c>
+      <c r="D33" s="164">
+        <f>D22*$C$10</f>
+        <v/>
+      </c>
+      <c r="E33" s="179">
+        <f>D22*$C$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="189" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C32" s="161">
-        <f>SUM(C26:C31)</f>
-        <v/>
-      </c>
-      <c r="D32" s="161">
-        <f>SUM(D26:D31)</f>
-        <v/>
-      </c>
-      <c r="E32" s="161">
-        <f>SUM(E26:E31)</f>
+      <c r="C34" s="161">
+        <f>SUM(C27:C33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="161">
+        <f>SUM(D27:D33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="161">
+        <f>SUM(E27:E33)</f>
         <v/>
       </c>
     </row>

--- a/docs/dataroom/sold-direct-model.xlsx
+++ b/docs/dataroom/sold-direct-model.xlsx
@@ -3187,16 +3187,16 @@
         <v>30</v>
       </c>
       <c r="D31" s="146" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="E31" s="146" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F31" s="146" t="n">
+        <v>475</v>
+      </c>
+      <c r="G31" s="146" t="n">
         <v>950</v>
-      </c>
-      <c r="G31" s="146" t="n">
-        <v>1900</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="118">
@@ -3209,16 +3209,16 @@
         <v>50</v>
       </c>
       <c r="D32" s="146" t="n">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="E32" s="146" t="n">
-        <v>650</v>
+        <v>325</v>
       </c>
       <c r="F32" s="146" t="n">
-        <v>1500</v>
+        <v>750</v>
       </c>
       <c r="G32" s="146" t="n">
-        <v>2900</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="118">
@@ -3231,16 +3231,16 @@
         <v>80</v>
       </c>
       <c r="D33" s="146" t="n">
-        <v>350</v>
+        <v>175</v>
       </c>
       <c r="E33" s="146" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="F33" s="146" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G33" s="146" t="n">
         <v>2400</v>
-      </c>
-      <c r="G33" s="146" t="n">
-        <v>4800</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="118">
@@ -3336,16 +3336,16 @@
         <v>4</v>
       </c>
       <c r="D42" s="146" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E42" s="146" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F42" s="146" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G42" s="146" t="n">
-        <v>96</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="118">
@@ -3505,16 +3505,16 @@
         <v>2500000</v>
       </c>
       <c r="D49" s="140" t="n">
-        <v>8000000</v>
+        <v>4000000</v>
       </c>
       <c r="E49" s="140" t="n">
-        <v>18000000</v>
+        <v>9000000</v>
       </c>
       <c r="F49" s="140" t="n">
-        <v>32000000</v>
+        <v>16000000</v>
       </c>
       <c r="G49" s="140" t="n">
-        <v>50000000</v>
+        <v>25000000</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="118">
@@ -7614,7 +7614,7 @@
         </is>
       </c>
       <c r="C8" s="214" t="n">
-        <v>250000000</v>
+        <v>125000000</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="118">
@@ -7624,7 +7624,7 @@
         </is>
       </c>
       <c r="C9" s="214" t="n">
-        <v>50000000</v>
+        <v>25000000</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="118">

--- a/docs/dataroom/sold-direct-model.xlsx
+++ b/docs/dataroom/sold-direct-model.xlsx
@@ -2591,14 +2591,14 @@
     <row r="15" ht="15" customHeight="1" s="118">
       <c r="B15" s="233" t="inlineStr">
         <is>
-          <t>AI-LEAN OPERATING MODEL:</t>
+          <t>TECHNOLOGY-LEAN OPERATING MODEL:</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="118">
       <c r="B16" s="231" t="inlineStr">
         <is>
-          <t>• 50% of headcount are AI agents (concierge/coordination/ops) at ~R0.15m/yr each vs ~R0.70-0.78m/yr fully-loaded human - roughly halves people-cost.</t>
+          <t>• 50% of headcount are automated roles (concierge/coordination/ops) at ~R0.15m/yr each vs ~R0.70-0.78m/yr fully-loaded human - roughly halves people-cost.</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2608,7 @@
     <row r="18" ht="15" customHeight="1" s="118">
       <c r="B18" s="233" t="inlineStr">
         <is>
-          <t>KEY SOURCED ANCHORS (full citations in docs/dataroom/00-assumptions.md):</t>
+          <t>KEY SOURCED ANCHORS (full citations in the Assumption base document in the data room):</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
     <row r="24" ht="15" customHeight="1" s="118">
       <c r="B24" s="231" t="inlineStr">
         <is>
-          <t>1. High margins (AI-lean + 1% take + sponsorship) - present a 'reinvest for growth' case. 2. AI agents at 50% of roles in Y1 is aggressive - validate with a pilot.</t>
+          <t>1. High margins (technology-lean + 1% take + sponsorship) - present a 'reinvest for growth' case. 2. automated roles at 50% of roles in Y1 is aggressive - validate with a pilot.</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
     <row r="1" ht="21" customHeight="1" s="118">
       <c r="B1" s="133" t="inlineStr">
         <is>
-          <t>Sold Direct — Model Assumptions (Prime · 1% fee · AI-lean · bank sponsor)</t>
+          <t>Sold Direct — Model Assumptions (Prime · 1% fee · technology-lean · bank sponsor)</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
     <row r="40" ht="15" customHeight="1" s="118">
       <c r="B40" s="135" t="inlineStr">
         <is>
-          <t>OPERATING EXPENSE INPUTS (BASE) — Y1–Y2 on the bootstrap operating stance (Oct 2026): four-person team, no office, Paysoft free-dev allocation</t>
+          <t>OPERATING EXPENSE INPUTS (BASE) — Y1–Y2: four-person launch team, no office, Paysoft free-dev allocation</t>
         </is>
       </c>
       <c r="C40" s="135" t="n"/>
@@ -3351,7 +3351,7 @@
     <row r="43" ht="15" customHeight="1" s="118">
       <c r="B43" s="136" t="inlineStr">
         <is>
-          <t>AI-agent share of headcount</t>
+          <t>Automated share of headcount</t>
         </is>
       </c>
       <c r="C43" s="137" t="n">
@@ -3400,7 +3400,7 @@
     <row r="45" ht="15" customHeight="1" s="118">
       <c r="B45" s="147" t="inlineStr">
         <is>
-          <t>AI agents</t>
+          <t>automated roles</t>
         </is>
       </c>
       <c r="C45" s="148">
@@ -3427,7 +3427,7 @@
     <row r="46" ht="15" customHeight="1" s="118">
       <c r="B46" s="136" t="inlineStr">
         <is>
-          <t>Human fully-loaded cost / FTE (R/yr) — Y1–Y2 bootstrap team: MD R50k · Marketing Director R50k · principal practitioner &amp; compliance R30k · agent/admin R20k per month, + statutory; Y2 adds 2 practitioners (R30k) + 2 agent/admin (R20k) against mandates</t>
+          <t>Human fully-loaded cost / FTE (R/yr) — Y1–Y2 launch team: MD R50k · Marketing Director R50k · principal practitioner &amp; compliance R30k · agent/admin R20k per month, + statutory; Y2 adds 2 practitioners (R30k) + 2 agent/admin (R20k) against mandates</t>
         </is>
       </c>
       <c r="C46" s="140" t="n">
@@ -3449,7 +3449,7 @@
     <row r="47" ht="15" customHeight="1" s="118">
       <c r="B47" s="136" t="inlineStr">
         <is>
-          <t>AI-agent run cost each (R/yr)</t>
+          <t>Automated-role run cost each (R/yr)</t>
         </is>
       </c>
       <c r="C47" s="140" t="n">
@@ -3471,7 +3471,7 @@
     <row r="48" ht="15" customHeight="1" s="118">
       <c r="B48" s="144" t="inlineStr">
         <is>
-          <t>Payroll + AI agents (R)</t>
+          <t>Payroll + automated roles (R)</t>
         </is>
       </c>
       <c r="C48" s="145">
@@ -4178,7 +4178,7 @@
     <row r="12" ht="15" customHeight="1" s="118">
       <c r="B12" s="124" t="inlineStr">
         <is>
-          <t>Payroll + AI agents</t>
+          <t>Payroll + automated roles</t>
         </is>
       </c>
       <c r="C12" s="154">
@@ -4514,7 +4514,7 @@
     <row r="27" ht="15" customHeight="1" s="118">
       <c r="B27" s="117" t="inlineStr">
         <is>
-          <t>Total headcount (human+AI)</t>
+          <t>Total headcount (people + automated roles)</t>
         </is>
       </c>
       <c r="C27" s="162">
@@ -4676,7 +4676,7 @@
     <row r="33" ht="15" customHeight="1" s="118">
       <c r="B33" s="117" t="inlineStr">
         <is>
-          <t>Payroll+AI % of revenue</t>
+          <t>Payroll + automation % of revenue</t>
         </is>
       </c>
       <c r="C33" s="165">
@@ -6287,7 +6287,7 @@
     <row r="2" ht="15" customHeight="1" s="118">
       <c r="B2" s="134" t="inlineStr">
         <is>
-          <t>Amber = input. Grey = calculated/linked. Estimates — see docs/dataroom/03-market-sizing.md for sources &amp; reliability.</t>
+          <t>Amber = input. Grey = calculated/linked. Estimates — sources in the Market sizing document in the data room.</t>
         </is>
       </c>
     </row>
@@ -6502,7 +6502,7 @@
       </c>
       <c r="D23" s="134" t="inlineStr">
         <is>
-          <t>ESTIMATE — broadens as avg price tapers; confirm</t>
+          <t>Estimate — broadens as the average price tapers</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="E6" s="213" t="inlineStr">
         <is>
-          <t>Four-person bootstrap team at R150k/month — founders at R50k each carry marketing, management, dealmaking, bookkeeping and tech support; hires beyond four only against signed mandates</t>
+          <t>Four-person launch team at R150k/month — founders at R50k each carry marketing, management, dealmaking, bookkeeping and tech support; hires beyond four only against signed mandates</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
     <row r="15" ht="15" customHeight="1" s="118">
       <c r="B15" s="134" t="inlineStr">
         <is>
-          <t>Note: the bootstrap stance (four-person team, no office) keeps the modelled cash trough small; most of the R5m is launch marketing and runway headroom in every scenario.</t>
+          <t>Note: the four-person launch team with no office keeps the modelled cash trough small; most of the R5m is launch marketing and runway headroom in every scenario.</t>
         </is>
       </c>
     </row>

--- a/docs/dataroom/sold-direct-model.xlsx
+++ b/docs/dataroom/sold-direct-model.xlsx
@@ -1750,7 +1750,7 @@
       <c r="B6" s="223" t="inlineStr">
         <is>
           <t>Traditional agencies
-(Pam Golding, Seeff, RE/MAX, Rawson)</t>
+(Pam Golding, Seeff, Rawson)</t>
         </is>
       </c>
       <c r="C6" s="213" t="inlineStr">

--- a/docs/dataroom/sold-direct-model.xlsx
+++ b/docs/dataroom/sold-direct-model.xlsx
@@ -3427,14 +3427,14 @@
     <row r="46" ht="15" customHeight="1" s="118">
       <c r="B46" s="136" t="inlineStr">
         <is>
-          <t>Human fully-loaded cost / FTE (R/yr) — Y1–Y2 launch team: MD R50k · Marketing Director R50k · principal practitioner &amp; compliance R30k · agent/admin R20k per month, + statutory; Y2 adds 2 practitioners (R30k) + 2 agent/admin (R20k) against mandates</t>
+          <t>Human fully-loaded cost / FTE (R/yr) — Y1–Y2 launch team: MD R60k · Marketing Director R60k · principal practitioner &amp; compliance R30k · agent/admin R20k per month, + statutory; Y2 adds 1 practitioner (R30k) + 1 agent/admin (R20k) against mandates</t>
         </is>
       </c>
       <c r="C46" s="140" t="n">
-        <v>462500</v>
+        <v>522500</v>
       </c>
       <c r="D46" s="140" t="n">
-        <v>381250</v>
+        <v>421250</v>
       </c>
       <c r="E46" s="140" t="n">
         <v>738000</v>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="E6" s="213" t="inlineStr">
         <is>
-          <t>Four-person launch team at R150k/month — founders at R50k each carry marketing, management, dealmaking, bookkeeping and tech support; hires beyond four only against signed mandates</t>
+          <t>Four-person launch team at R170k/month — founders at R60k each for a 120-hour-a-month commitment carry marketing, management, dealmaking, bookkeeping and tech support; hires beyond four only against signed mandates</t>
         </is>
       </c>
     </row>
@@ -7560,7 +7560,7 @@
     <row r="2" ht="15" customHeight="1" s="118">
       <c r="B2" s="134" t="inlineStr">
         <is>
-          <t>No separate founding round — the Strategic Funder and the technology partner come in at inception alongside the working founders. Johannes le Roux 32.5% · Dean Kruger 32.5% · Paysoft (technology partner, vesting against preferred rates + free development) 10% · option pool (reserved) 4% · board seat (reserved, non-executive) 1% · Strategic Funder R5m for 20% (R20m pre / R25m post). Founder shares reverse-vest over 36 months. Amber = editable inputs; round economics linked from Capital &amp; Valuation.</t>
+          <t>No separate founding round — the Strategic Funder and the technology partner come in at inception alongside the working founders. Johannes le Roux 32.5% · Dean Kruger 32.5% · Paysoft (technology partner, vesting against preferred rates + free development) 10% · option pool (reserved) 4% · board seat (reserved, non-executive) 1% · Strategic Funder R5m for 20% (R20m pre / R25m post). Amber = editable inputs; round economics linked from Capital &amp; Valuation.</t>
         </is>
       </c>
     </row>
